--- a/Results/S6.xlsx
+++ b/Results/S6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ppaer_2\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0CD52E-B2CB-458F-BC9E-AF406D79582F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A8D619-ABD4-44CD-9CAA-7E61E73DFD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="720" windowWidth="19560" windowHeight="15480" xr2:uid="{F5F58990-9793-4A8C-927D-D73CA3CDA898}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F5F58990-9793-4A8C-927D-D73CA3CDA898}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="65">
   <si>
     <t>Model</t>
   </si>
@@ -152,127 +152,85 @@
     <t>LightGBM</t>
   </si>
   <si>
-    <t>Table 1: Granular Trait-specific Sparsity (\%) Comparison across Four Genomic Datasets using Non-convex Regularizers, including Baseline Comparisons.</t>
-  </si>
-  <si>
     <t>SNP Input</t>
   </si>
   <si>
     <t>Proximal</t>
   </si>
   <si>
-    <t>Mice T1 MSE</t>
-  </si>
-  <si>
-    <t>Mice T1 dCor</t>
-  </si>
-  <si>
-    <t>Mice T2 MSE</t>
-  </si>
-  <si>
-    <t>Mice T2 dCor</t>
-  </si>
-  <si>
-    <t>Pig T1 MSE</t>
-  </si>
-  <si>
-    <t>Pig T1 dCor</t>
-  </si>
-  <si>
-    <t>Pig T2 MSE</t>
-  </si>
-  <si>
-    <t>Pig T2 dCor</t>
-  </si>
-  <si>
-    <t>Pig T3 MSE</t>
-  </si>
-  <si>
-    <t>Pig T3 dCor</t>
-  </si>
-  <si>
-    <t>Pig T4 MSE</t>
-  </si>
-  <si>
-    <t>Pig T4 dCor</t>
-  </si>
-  <si>
-    <t>Pig T5 MSE</t>
-  </si>
-  <si>
-    <t>Pig T5 dCor</t>
-  </si>
-  <si>
-    <t>Wheat T1 MSE</t>
-  </si>
-  <si>
-    <t>Wheat T1 dCor</t>
-  </si>
-  <si>
-    <t>Wheat T2 MSE</t>
-  </si>
-  <si>
-    <t>Wheat T2 dCor</t>
-  </si>
-  <si>
-    <t>Wheat T3 MSE</t>
-  </si>
-  <si>
-    <t>Wheat T3 dCor</t>
-  </si>
-  <si>
-    <t>Wheat T4 MSE</t>
-  </si>
-  <si>
-    <t>Wheat T4 dCor</t>
-  </si>
-  <si>
-    <t>Pine T1 MSE</t>
-  </si>
-  <si>
-    <t>Pine T1 dCor</t>
-  </si>
-  <si>
-    <t>Pine T2 MSE</t>
-  </si>
-  <si>
-    <t>Pine T2 dCor</t>
-  </si>
-  <si>
-    <t>Pine T3 MSE</t>
-  </si>
-  <si>
-    <t>Pine T3 dCor</t>
-  </si>
-  <si>
-    <t>Pine T4 MSE</t>
-  </si>
-  <si>
-    <t>Pine T4 dCor</t>
-  </si>
-  <si>
-    <t>Pine T5 MSE</t>
-  </si>
-  <si>
-    <t>Pine T5 dCor</t>
-  </si>
-  <si>
-    <t>Pine T6 MSE</t>
-  </si>
-  <si>
-    <t>Pine T6 dCor</t>
-  </si>
-  <si>
-    <t>Pine T7 MSE</t>
-  </si>
-  <si>
-    <t>Pine T7 dCor</t>
-  </si>
-  <si>
     <t>All SNPs</t>
   </si>
   <si>
     <t>Info SNPs</t>
+  </si>
+  <si>
+    <t>Table 1: Granular Trait-specific Sparsity (\%) Comparison across Four Genomic Datasets using non-convex regularizers, including baseline comparisons.</t>
+  </si>
+  <si>
+    <t>T1 MSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> T1 dCor</t>
+  </si>
+  <si>
+    <t>T2 MSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> T2 dCor</t>
+  </si>
+  <si>
+    <t>T3 MSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> T3 dCor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> T4 MSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> T4 dCor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> T5 MSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> T5 dCor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> T6 MSE</t>
+  </si>
+  <si>
+    <t>T6 dCor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> T7 MSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> T7 dCor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> T1 MSE</t>
+  </si>
+  <si>
+    <t>T1 dCor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> T3 MSE</t>
+  </si>
+  <si>
+    <t>T4 MSE</t>
+  </si>
+  <si>
+    <t>T5 dCor</t>
+  </si>
+  <si>
+    <t>T3 dCor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> T2 MSE</t>
+  </si>
+  <si>
+    <t>Comparison between different SNP input:  ALL SNPs vs. Info SNPs selected by the best regularizer L_1/2</t>
   </si>
 </sst>
 </file>
@@ -302,7 +260,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -310,23 +268,96 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -663,66 +694,70 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{364C985D-F4D5-43F4-A60E-7CF5E91D0CDC}">
   <dimension ref="A2:AL24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="21" max="21" width="9.7109375" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4" t="s">
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="1" t="s">
@@ -780,7 +815,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
@@ -842,7 +877,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -904,7 +939,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
@@ -966,7 +1001,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
@@ -1028,7 +1063,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
@@ -1090,7 +1125,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
@@ -1152,7 +1187,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
@@ -1214,7 +1249,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>37</v>
       </c>
@@ -1276,9 +1311,55 @@
         <v>22.4</v>
       </c>
     </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="9"/>
+      <c r="AA16" s="9"/>
+      <c r="AB16" s="9"/>
+      <c r="AC16" s="9"/>
+      <c r="AD16" s="9"/>
+      <c r="AE16" s="9"/>
+      <c r="AF16" s="9"/>
+      <c r="AG16" s="9"/>
+      <c r="AH16" s="9"/>
+      <c r="AI16" s="9"/>
+      <c r="AJ16" s="9"/>
+      <c r="AK16" s="9"/>
+      <c r="AL16" s="9"/>
+    </row>
     <row r="17" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="A17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="3" t="s">
         <v>2</v>
       </c>
@@ -1325,126 +1406,122 @@
       <c r="AL17" s="3"/>
     </row>
     <row r="18" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="1" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="I18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="T18" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="U18" s="1" t="s">
         <v>59</v>
       </c>
       <c r="V18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W18" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="W18" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="X18" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="AA18" s="1" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="AC18" s="1" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AD18" s="1" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="AF18" s="1" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="AH18" s="1" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="AI18" s="1" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="AJ18" s="1" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="AK18" s="1" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AL18" s="1" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="5">
+      <c r="A19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="2">
         <v>0</v>
       </c>
       <c r="C19" s="1">
@@ -1557,7 +1634,8 @@
       </c>
     </row>
     <row r="20" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="B20" s="5">
+      <c r="A20" s="7"/>
+      <c r="B20" s="2">
         <v>0.5</v>
       </c>
       <c r="C20" s="1">
@@ -1670,7 +1748,8 @@
       </c>
     </row>
     <row r="21" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="B21" s="5">
+      <c r="A21" s="8"/>
+      <c r="B21" s="2">
         <v>1</v>
       </c>
       <c r="C21" s="1">
@@ -1783,10 +1862,10 @@
       </c>
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B22" s="5">
+      <c r="A22" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="2">
         <v>0</v>
       </c>
       <c r="C22" s="1">
@@ -1899,7 +1978,8 @@
       </c>
     </row>
     <row r="23" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="B23" s="5">
+      <c r="A23" s="7"/>
+      <c r="B23" s="2">
         <v>0.5</v>
       </c>
       <c r="C23" s="1">
@@ -2012,7 +2092,8 @@
       </c>
     </row>
     <row r="24" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="B24" s="5">
+      <c r="A24" s="8"/>
+      <c r="B24" s="2">
         <v>1</v>
       </c>
       <c r="C24" s="1">
@@ -2125,7 +2206,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="16">
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A16:AL16"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="G17:P17"/>
     <mergeCell ref="Q17:X17"/>
